--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487743_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487743_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.224</v>
+        <v>6.6774</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4318</v>
+        <v>4.5309</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7922</v>
+        <v>2.1465</v>
       </c>
       <c r="G2" t="n">
         <v>2.6132</v>
@@ -610,13 +610,13 @@
         <v>3.2985</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7958</v>
+        <v>0.2493</v>
       </c>
       <c r="T2" t="n">
-        <v>1.227</v>
+        <v>0.3261</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4311</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.5164</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5995</v>
+        <v>4.6545</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4304</v>
+        <v>1.7307</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1691</v>
+        <v>2.9238</v>
       </c>
       <c r="G3" t="n">
         <v>3.3482</v>
@@ -688,13 +688,13 @@
         <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4069</v>
+        <v>-0.3519</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7874</v>
+        <v>-0.4871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3805</v>
+        <v>0.1352</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8547</v>
+        <v>3.7704</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5968</v>
+        <v>1.2793</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4515</v>
+        <v>2.4911</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0178</v>
+        <v>3.152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3188</v>
+        <v>1.9163</v>
       </c>
       <c r="I4" t="n">
-        <v>1.699</v>
+        <v>1.2357</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3907</v>
+        <v>3.6707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08649999999999999</v>
+        <v>2.2904</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3041</v>
+        <v>1.3803</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6271</v>
+        <v>-0.5187</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2323</v>
+        <v>-0.374</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3948</v>
+        <v>-0.1446</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
         <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8668</v>
+        <v>0.0064</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0471</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9139</v>
+        <v>0.0993</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9701</v>
+        <v>3.4548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7788</v>
+        <v>-0.6969</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1913</v>
+        <v>4.1517</v>
       </c>
       <c r="G5" t="n">
-        <v>3.152</v>
+        <v>2.0178</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9163</v>
+        <v>0.3188</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2357</v>
+        <v>1.699</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6707</v>
+        <v>1.3907</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2904</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3803</v>
+        <v>1.3041</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5187</v>
+        <v>0.6271</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.374</v>
+        <v>0.2323</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1446</v>
+        <v>0.3948</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
         <v>2.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7939000000000001</v>
+        <v>0.4669</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5933</v>
+        <v>-0.1472</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2005</v>
+        <v>0.6141</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6756</v>
+        <v>3.1667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8881</v>
+        <v>1.1884</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7875</v>
+        <v>1.9783</v>
       </c>
       <c r="G6" t="n">
         <v>2.6724</v>
@@ -922,13 +922,13 @@
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4908</v>
+        <v>0.0003</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7874</v>
+        <v>-0.4871</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2966</v>
+        <v>0.4873</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4566</v>
+        <v>2.9299</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.794</v>
+        <v>-0.2935</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2506</v>
+        <v>3.2233</v>
       </c>
       <c r="G7" t="n">
         <v>-0.839</v>
@@ -1000,13 +1000,13 @@
         <v>2.7164</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5879</v>
+        <v>-0.1147</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.775</v>
+        <v>-0.2745</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1871</v>
+        <v>0.1598</v>
       </c>
       <c r="V7" t="n">
         <v>3.1075</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8606</v>
+        <v>1.76</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6502</v>
+        <v>1.2498</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2105</v>
+        <v>0.5103</v>
       </c>
       <c r="G8" t="n">
         <v>0.6166</v>
@@ -1078,13 +1078,13 @@
         <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>0.9494</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5473</v>
+        <v>0.1469</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5027</v>
+        <v>0.8025</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6102</v>
+        <v>1.0424</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3983</v>
+        <v>-2.7098</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0085</v>
+        <v>3.7522</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.451</v>
+        <v>0.9114</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8832</v>
+        <v>0.0305</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5678</v>
+        <v>0.8809</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4714</v>
+        <v>-0.2552</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.2018</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1218</v>
+        <v>-0.0533</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9796</v>
+        <v>1.1666</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.29</v>
+        <v>0.2323</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6896</v>
+        <v>0.9343</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>3.1045</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8374</v>
+        <v>0.1907</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7896</v>
+        <v>-0.5143</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0478</v>
+        <v>0.7049</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2239</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0875</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.91</v>
+        <v>-0.2684</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9974</v>
+        <v>1.0935</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9114</v>
+        <v>-1.1091</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0305</v>
+        <v>-0.5413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8809</v>
+        <v>-0.5678</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2552</v>
+        <v>0.0765</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2018</v>
+        <v>-0.0453</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0533</v>
+        <v>0.1218</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1666</v>
+        <v>-1.1856</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2323</v>
+        <v>-0.496</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9343</v>
+        <v>-0.6896</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1045</v>
+        <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2358</v>
+        <v>0.3819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7145</v>
+        <v>-0.3449</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9502</v>
+        <v>0.7268</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7339</v>
+        <v>0.6642</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4686</v>
+        <v>-1.099</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2025</v>
+        <v>1.7632</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1091</v>
+        <v>-1.451</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5413</v>
+        <v>-0.8832</v>
       </c>
       <c r="I11" t="n">
         <v>-0.5678</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0765</v>
+        <v>-0.4714</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0453</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>0.1218</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1856</v>
+        <v>-0.9796</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.496</v>
+        <v>-0.29</v>
       </c>
       <c r="O11" t="n">
         <v>-0.6896</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5523</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2907</v>
+        <v>0.8914</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8358</v>
+        <v>0.8025</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3013</v>
+        <v>0.2379</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0814</v>
+        <v>0.0187</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3828</v>
+        <v>0.2192</v>
       </c>
       <c r="G12" t="n">
         <v>0.3139</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1815</v>
+        <v>0.118</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3632</v>
+        <v>0.1996</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.5084</v>
       </c>
       <c r="E13" t="n">
         <v>0.3349</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.034</v>
+        <v>-0.8433</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2826</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3091</v>
+        <v>-0.1183</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0063</v>
+        <v>0.1845</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2716</v>
@@ -1507,7 +1507,7 @@
         <v>5.265099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>23.4099</v>
+        <v>23.4098</v>
       </c>
       <c r="G14" t="n">
         <v>11.9638</v>
@@ -1522,7 +1522,7 @@
         <v>15.1464</v>
       </c>
       <c r="K14" t="n">
-        <v>6.220299999999999</v>
+        <v>6.2203</v>
       </c>
       <c r="L14" t="n">
         <v>8.926</v>
@@ -1552,7 +1552,7 @@
         <v>-2.1704</v>
       </c>
       <c r="U14" t="n">
-        <v>4.8399</v>
+        <v>4.839700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.4</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1895</v>
+        <v>1.8307</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8086</v>
+        <v>4.292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6191</v>
+        <v>-2.4614</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1822</v>
+        <v>6.4484</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3213</v>
+        <v>2.6323</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5035</v>
+        <v>3.8161</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9068</v>
+        <v>7.1953</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6591</v>
+        <v>2.278</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2477</v>
+        <v>4.9172</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7246</v>
+        <v>-0.7469</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9804</v>
+        <v>0.3542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2558</v>
+        <v>-1.1011</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-2.1344</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1882</v>
+        <v>-0.752</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4116</v>
+        <v>-0.7689</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2234</v>
+        <v>0.0168</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3299</v>
+        <v>-3.6716</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.894</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0064</v>
+        <v>1.3169</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0919</v>
+        <v>1.9087</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0854</v>
+        <v>-0.5918</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4484</v>
+        <v>3.1822</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6323</v>
+        <v>-0.3213</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8161</v>
+        <v>3.5035</v>
       </c>
       <c r="J16" t="n">
-        <v>7.1953</v>
+        <v>3.9068</v>
       </c>
       <c r="K16" t="n">
-        <v>2.278</v>
+        <v>0.6591</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9172</v>
+        <v>3.2477</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7469</v>
+        <v>-0.7246</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3542</v>
+        <v>-0.9804</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1011</v>
+        <v>0.2558</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5763</v>
+        <v>-0.0608</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9691</v>
+        <v>-0.3115</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6072</v>
+        <v>0.2507</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.6716</v>
+        <v>0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.6716</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.277</v>
+        <v>-0.2864</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1084</v>
+        <v>1.9082</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3854</v>
+        <v>-2.1946</v>
       </c>
       <c r="G17" t="n">
         <v>-2.9926</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2977</v>
+        <v>0.2882</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4374</v>
+        <v>0.2372</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V17" t="n">
         <v>1.8358</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9619</v>
+        <v>-1.6104</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2012</v>
+        <v>-3.6016</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2393</v>
+        <v>1.9912</v>
       </c>
       <c r="G18" t="n">
         <v>-1.228</v>
@@ -1858,13 +1858,13 @@
         <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2661</v>
+        <v>-0.3824</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3623</v>
+        <v>-0.7627</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6283</v>
+        <v>0.3802</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1258</v>
+        <v>-2.2104</v>
       </c>
       <c r="E19" t="n">
         <v>-4.9644</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8386</v>
+        <v>2.7541</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5023</v>
@@ -1936,13 +1936,13 @@
         <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5951</v>
+        <v>-0.6797</v>
       </c>
       <c r="T19" t="n">
         <v>-1.0296</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4345</v>
+        <v>0.35</v>
       </c>
       <c r="V19" t="n">
         <v>0.9418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7183</v>
+        <v>-2.2846</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0792</v>
+        <v>-1.7789</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6391</v>
+        <v>-0.5057</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1713</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4127</v>
+        <v>0.021</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6539</v>
+        <v>-0.3536</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2412</v>
+        <v>0.3746</v>
       </c>
       <c r="V20" t="n">
         <v>0.6119</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8838</v>
+        <v>-2.7292</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1214</v>
+        <v>-2.0213</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7624</v>
+        <v>-0.7079</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5137</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2059</v>
+        <v>-0.0513</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0337</v>
+        <v>-3.8246</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7672</v>
+        <v>-4.6671</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7335</v>
+        <v>0.8425</v>
       </c>
       <c r="G22" t="n">
         <v>-2.733</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0186</v>
+        <v>-0.8095</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0296</v>
+        <v>-0.9295</v>
       </c>
       <c r="U22" t="n">
-        <v>0.011</v>
+        <v>0.12</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9383</v>
+        <v>-4.6474</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4139</v>
+        <v>-2.3138</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5244</v>
+        <v>-2.3336</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6296</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1027</v>
+        <v>0.1881</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.4327</v>
       </c>
       <c r="U23" t="n">
-        <v>0.43</v>
+        <v>0.6208</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.991</v>
+        <v>-5.1123</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6248</v>
+        <v>-4.825</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3663</v>
+        <v>-0.2873</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2534</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3033</v>
+        <v>-0.4245</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2412</v>
+        <v>-0.4414</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0621</v>
+        <v>0.0168</v>
       </c>
       <c r="V24" t="n">
         <v>1.506</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9411</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.2466</v>
+        <v>-7.3467</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6945</v>
+        <v>-1.1033</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5705</v>
@@ -2404,13 +2404,13 @@
         <v>1.1642</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1698</v>
+        <v>0.6609</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1951</v>
+        <v>0.095</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9747</v>
+        <v>0.5659</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6597</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.675</v>
+        <v>-28.0077</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.4098</v>
+        <v>-23.4099</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.265199999999999</v>
+        <v>-4.597799999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-11.9638</v>
@@ -2482,13 +2482,13 @@
         <v>15.5224</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6692</v>
+        <v>-2.002</v>
       </c>
       <c r="T26" t="n">
         <v>-4.8399</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1704</v>
+        <v>2.8376</v>
       </c>
       <c r="V26" t="n">
         <v>-2.3999</v>
